--- a/data/raw/sales/Week 16/White_Mulberry/amazon_sales.xlsx
+++ b/data/raw/sales/Week 16/White_Mulberry/amazon_sales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 16\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C317AC87-9633-4C61-9280-EAA5BF1959F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A455E4-C6EA-4547-A427-39324B9C5ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -801,7 +801,9 @@
   <dimension ref="A1:X30"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="9.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
